--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>46164</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45063</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>46028</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>46061</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44974</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>45490</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>45601</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>46121</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>45688</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>45447</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46283</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46073</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46168</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>44890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>44613</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44692</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44481</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44874</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44480</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44627</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44685</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44722</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44518</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44459</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44861</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44474</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44469</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44540</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44508</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>45093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>45218</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45751</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45092</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45265</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45667</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>44958</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>45097</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>45218</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45736</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44495</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45265</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44736</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>45028</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>45663</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>45190</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>45090</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>45245</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>45222</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>45754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44979</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45159</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44734</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>45736</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45119</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         <v>45119</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>45119</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>44588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         <v>44754</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>45190</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>45191</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>45231</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44813</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45194</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45174</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>44775</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45279</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45180</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>45365</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45254</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>44965</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45737</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>44865</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45093</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45106</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>46139</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45119</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>44964</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45884</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45159</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45159</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45926</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45197</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45250</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45890</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44798</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45891</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45742</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45926</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45376</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>46136</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45734</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>46139</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>44900</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45908</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45169</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>46141</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>46141</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>45504</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>45215</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45849</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45211</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>46141</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>46141</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44861</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45923</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45922</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45923</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45315</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45926</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45926</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44796</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45926</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45926</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45399</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45684</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>45926</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13160,7 +13160,7 @@
         <v>45926</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>45926</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44531</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45701</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>44937</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>45180</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>46150</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45426</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>46150</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>46150</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>44518</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45546</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45961</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>45106</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>45194</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>44862</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44953</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>45188</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45974</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45601</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45974</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45629</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>44901</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45667</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45985</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44984</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45159</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>46161</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>46163</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44928</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>44805</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45257</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>45119</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>46003</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>46003</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>46003</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>46164</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44883</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>46003</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45194</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46008</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>46008</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45190</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>46010</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44956</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>44911</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45282</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         <v>44517</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>44966</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>46171</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>46174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>44984</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45215</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>45058</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45684</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>46050</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45344</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>46055</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45058</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>46055</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>46055</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>46056</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>46059</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44956</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46059</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>46061</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46062</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>46062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46062</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>46153</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>46069</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>44711</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45218</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46183</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>46183</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>46183</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46079</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>46183</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>46183</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>44618</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>46183</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45293</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>46183</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>46084</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>46084</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45181</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>44469</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45208</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>46155</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>46196</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>46100</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>46101</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46101</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46106</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46111</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>46111</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44951</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>45187</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>45187</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>46111</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>46111</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>46111</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45295</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>44966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45061</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45684</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45215</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21270,7 +21270,7 @@
         <v>45295</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45489</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21416,7 +21416,7 @@
         <v>44890</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21489,7 +21489,7 @@
         <v>46134</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45838</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45756</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21708,7 +21708,7 @@
         <v>45239</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45055</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45055</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45169</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
         <v>45782</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45692</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>46206</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>46248</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45250</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45181</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45586</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44994</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44965</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45737</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45174</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>44572</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44593</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22964,7 +22964,7 @@
         <v>45737</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>44753</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45595</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>46258</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>46258</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45174</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>46171</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23485,7 +23485,7 @@
         <v>45297</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45379</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45097</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>44888</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>45194</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23850,7 +23850,7 @@
         <v>46219</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23923,7 +23923,7 @@
         <v>45180</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45687</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45707</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>46219</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45055</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45297</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45701</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>46227</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45737</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45737</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46227</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>46227</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24887,7 +24887,7 @@
         <v>45700</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24960,7 +24960,7 @@
         <v>44984</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>45222</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>45504</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>45504</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>45435</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45601</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45692</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         <v>45504</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25544,7 +25544,7 @@
         <v>45504</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45792</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45257</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45797</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45797</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>46241</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>46241</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45685</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45692</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>44939</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45742</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45817</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>45817</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45818</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45791</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>45849</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45849</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45586</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45876</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>45876</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45610</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45567</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45246</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45426</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>45195</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>46168</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44866</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46164</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>44761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>46028</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46061</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>46121</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45295</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45447</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45601</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45688</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44974</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>46283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45490</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46073</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46168</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>44890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>44613</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44692</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44481</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44874</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44480</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44627</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44685</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44722</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44518</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44861</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44474</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44540</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45737</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45231</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45215</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45093</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45297</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>45106</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45489</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44984</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44984</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45174</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45365</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>45797</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45884</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45797</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45295</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45891</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44900</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>45685</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>46050</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45908</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>46055</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>46055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>46055</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>46056</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46055</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>46062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>46059</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>46062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45742</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>46061</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>46062</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>45922</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44888</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>45692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>46069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45923</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>45923</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45926</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45926</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45926</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45926</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45926</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>46079</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44911</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44939</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>46084</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>46084</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>45614</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45344</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>46100</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>46101</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>46101</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>46106</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44572</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44736</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45315</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>46111</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>46111</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>46111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45293</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45736</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44956</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45961</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44958</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45106</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45974</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45817</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44956</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45663</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>44734</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45926</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45985</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45926</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46136</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45734</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>46134</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44798</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45838</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45818</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44495</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45692</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45782</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>46003</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>46003</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>46003</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>46003</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46139</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45751</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>46008</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>46010</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45190</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>46139</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45055</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44865</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>46141</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>46141</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>46141</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>46141</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45849</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45426</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>46150</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>46150</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>46150</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45791</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45737</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45754</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45119</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46161</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44517</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45684</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>46163</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46164</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45849</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45586</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46171</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45586</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44966</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>46174</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45601</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>46153</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44964</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45180</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46183</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45174</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45399</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>46183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>46183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45379</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>46155</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45876</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>46196</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>44862</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44813</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45191</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45737</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45737</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45737</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45159</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45181</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45097</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45667</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45093</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46206</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45055</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45092</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45684</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>45215</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45119</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45190</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44593</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46258</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45701</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>46258</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44618</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44711</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45211</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45197</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45684</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45174</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45239</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46219</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45250</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45250</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45187</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45169</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45159</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45159</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44754</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45297</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45254</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>46227</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>46227</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>46227</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45736</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44883</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45187</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44775</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45197</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45194</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>44965</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45218</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>46241</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>46241</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45282</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45194</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44951</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45215</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>44518</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>44890</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45180</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46248</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44753</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>44861</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45061</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44978</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44469</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45090</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45218</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45245</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45707</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45119</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45504</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45169</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44901</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45629</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45180</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45194</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45295</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45028</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45218</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44928</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44796</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>44588</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45595</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44508</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45376</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>44965</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45257</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45208</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45687</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45181</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45667</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45700</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45504</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45504</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45435</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45692</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45222</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45184</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>45601</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45504</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45790</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>44984</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45504</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45792</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45610</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>45567</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45426</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46168</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44866</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46164</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>44761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>46028</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46061</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>45875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>46079</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>46121</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45295</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45447</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>45601</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45688</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44974</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>46283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>45478</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45490</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46073</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46168</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         <v>44862</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>44890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>44613</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>44678</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>44692</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>44481</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44874</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>44480</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44627</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44685</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44882</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44722</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44491</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44722</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44874</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44518</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44861</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44474</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44540</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>45737</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>45231</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45215</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>45093</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>45297</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>45106</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44805</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45119</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45489</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44984</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44984</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>45279</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45174</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45365</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>45797</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45884</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45797</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44979</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45295</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45891</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44900</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>45685</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>46050</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45908</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>46055</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>46055</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>46055</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>46056</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>46055</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>46062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>46059</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>46062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45742</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>46061</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>46062</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>46059</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>45546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>45922</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>44888</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>45692</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>46069</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45923</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>45923</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>45926</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45926</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>45926</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45926</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>45926</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>46079</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44911</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>44939</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10464,7 +10464,7 @@
         <v>46084</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>46084</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>45614</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>45344</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>46100</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>46101</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>46101</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>46106</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44572</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44736</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45315</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>46111</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>46111</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>46111</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46111</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45293</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45736</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44956</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>45961</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44958</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45106</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>45974</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>45817</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>45817</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>44956</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45663</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>44734</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45926</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45985</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45926</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>46136</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45734</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>46134</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44798</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45838</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45818</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44495</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45742</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45692</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45782</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>45701</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>46003</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>46003</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>46003</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>46003</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>46139</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>46008</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45751</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>46008</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>46010</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14489,7 +14489,7 @@
         <v>45190</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>44953</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45058</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>46139</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45055</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>44865</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>46141</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>46141</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         <v>46141</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>46141</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45849</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45426</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>46150</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>46150</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15511,7 +15511,7 @@
         <v>46150</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>45791</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45737</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>45754</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45119</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>46161</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>44517</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45684</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16105,7 +16105,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>46163</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>46164</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45849</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45849</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>45586</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46171</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45586</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44966</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>46174</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>45601</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16923,7 +16923,7 @@
         <v>46153</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44964</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45180</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>44937</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>46183</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46183</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>45174</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>46183</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17512,7 +17512,7 @@
         <v>45399</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17731,7 +17731,7 @@
         <v>46183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17804,7 +17804,7 @@
         <v>46183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>45379</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17950,7 +17950,7 @@
         <v>46155</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45876</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>46196</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>44862</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>44813</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45191</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>45737</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45737</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45737</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>45159</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>45181</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45097</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>45667</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45093</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46206</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45055</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45092</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45684</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>45215</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45119</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>45190</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44593</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46258</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45701</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>46258</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44618</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44711</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45211</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46171</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45197</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45684</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45174</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45239</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>46219</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46219</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45250</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20696,7 +20696,7 @@
         <v>45250</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45187</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45169</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45159</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45159</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>44754</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45297</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45254</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>46227</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>46227</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>46227</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45736</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>44883</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45187</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>44775</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45197</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45194</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>44965</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45218</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>46241</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>44531</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>46241</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>45282</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45194</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>44951</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45215</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>44518</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>44890</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45180</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>46248</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>44753</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>44861</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45061</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44978</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45097</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44469</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45090</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45218</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45245</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45707</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45119</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45504</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45169</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>44901</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45629</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45180</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45194</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45295</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45028</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45218</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45055</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24809,7 +24809,7 @@
         <v>45055</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         <v>45190</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>45194</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44928</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>44796</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45265</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>44588</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45595</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25393,7 +25393,7 @@
         <v>44508</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45376</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>44965</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45188</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45257</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45208</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45687</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45181</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45667</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45700</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45504</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>45504</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>45435</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>45692</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>45222</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>45184</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26566,7 +26566,7 @@
         <v>45601</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45504</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26712,7 +26712,7 @@
         <v>45790</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26785,7 +26785,7 @@
         <v>44984</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26858,7 +26858,7 @@
         <v>45504</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45792</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45610</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>45567</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45426</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46168</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>46164</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>46028</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46061</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45875</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45211</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44974</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>46079</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>46121</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>45601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>46283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45447</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46168</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44890</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44678</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44692</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44481</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44874</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44480</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>44627</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>44685</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>44831</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>44567</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44722</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44518</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44861</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>44474</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45093</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45218</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>45265</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45751</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>45504</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45504</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44495</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>45055</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>46003</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>45435</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>45601</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>45504</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>46003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45667</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>45097</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45218</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44958</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>45736</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>46003</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45790</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45028</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>46008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45265</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44736</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45891</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45190</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45090</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45908</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45792</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45257</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45797</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45797</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45685</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>45222</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45159</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44754</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45692</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>46050</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>46055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>46055</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45923</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>46055</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>46056</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45926</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45926</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45926</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>46059</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45926</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45926</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>46059</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45754</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44979</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>46061</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>46062</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>46062</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44734</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45736</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45119</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45119</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45119</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>46069</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45190</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45231</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44813</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>46079</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45194</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>46084</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45961</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45279</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45180</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>46100</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45974</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45817</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45817</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46106</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45818</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>46111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>46111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45365</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45254</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45737</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44865</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45093</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45119</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44964</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45159</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45159</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45250</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>45791</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45756</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45376</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45782</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45169</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45169</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>46139</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45849</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45849</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45926</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45504</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45215</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44861</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45926</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45315</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>46136</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45734</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44796</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46139</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45399</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45684</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45586</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>46141</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45701</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>46141</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44937</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45849</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>46141</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>46141</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45180</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45426</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>44518</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>46150</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>46150</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>46150</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45546</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45106</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45194</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44862</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>46161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45188</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>46163</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45601</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45876</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45629</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45876</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46164</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45667</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44984</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45159</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>46171</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46174</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45884</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>46153</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>46183</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>46183</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>46183</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46183</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46183</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44928</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46183</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46183</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44805</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45257</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45119</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44883</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>46155</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45194</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45190</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>46196</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44956</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44911</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45282</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44517</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>44966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46206</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>44978</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44984</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45215</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45058</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45684</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>46258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>46258</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>46171</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45344</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45058</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46219</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44956</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>46219</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44711</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45218</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46227</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>46227</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>46227</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>44618</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45208</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>46241</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45614</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>46241</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>44951</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45187</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45187</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45295</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44966</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45061</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>46248</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45215</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45295</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45489</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44890</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45055</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45692</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>45181</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45926</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45586</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44965</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>45737</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45174</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44572</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44593</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45737</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44753</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45595</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45297</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45379</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44888</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>45194</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45180</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45687</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45197</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45055</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45297</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45701</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45737</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45737</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45700</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44984</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45610</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45567</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45246</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45426</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45195</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>46168</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>46164</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>44973</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>46028</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46061</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45875</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45211</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>44974</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>46079</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>46121</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>45490</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>45601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         <v>46283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>45447</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>46168</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>44862</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44890</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>44678</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>44692</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44481</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44862</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v>44874</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>44480</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>44627</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>44685</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         <v>44831</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>44567</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>44491</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44722</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>44874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44518</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44861</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>44474</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>45092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44508</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45093</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45218</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>45265</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45751</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45222</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>45504</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>45504</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>44495</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>45055</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>46003</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>45435</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>45601</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>45504</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>45504</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>46003</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>45667</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>45097</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>45218</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45184</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>44958</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>45736</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
         <v>46003</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45790</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>45028</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>46008</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>46008</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         <v>45265</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>44736</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>45891</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45190</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45090</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>45908</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>45792</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>45257</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>45797</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45797</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>45685</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>45222</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>45159</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44754</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>45692</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>46050</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>46055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>45922</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>44939</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>46055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>46055</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>45923</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>46055</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>46056</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>45926</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>45926</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45926</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>46059</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45926</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45926</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10845,7 +10845,7 @@
         <v>46059</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45754</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44979</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>46061</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>46062</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>46062</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>46062</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44734</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>45736</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45119</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45119</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45119</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>46069</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>44588</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>45190</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45231</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45191</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44813</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12174,7 +12174,7 @@
         <v>46079</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12252,7 +12252,7 @@
         <v>45194</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>46084</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
         <v>45174</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>45961</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45742</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>44775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45279</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45180</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>46100</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45974</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45817</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>45817</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46106</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>45818</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>46111</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13498,7 +13498,7 @@
         <v>46111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>45985</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13644,7 +13644,7 @@
         <v>46111</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>46111</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45365</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45254</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44965</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45737</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44865</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14160,7 +14160,7 @@
         <v>45093</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>45106</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45119</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44964</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45159</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45159</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45197</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>45250</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>45791</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44798</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>46134</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45838</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45756</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45376</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45782</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>44900</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45169</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45169</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>46139</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>44917</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45849</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>45849</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15844,7 +15844,7 @@
         <v>45926</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>45504</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45215</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>45211</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>44861</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45926</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16282,7 +16282,7 @@
         <v>45315</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>46136</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16428,7 +16428,7 @@
         <v>45734</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44796</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>46139</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16647,7 +16647,7 @@
         <v>45399</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16720,7 +16720,7 @@
         <v>45684</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45586</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>44531</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>46141</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17012,7 +17012,7 @@
         <v>45701</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17085,7 +17085,7 @@
         <v>46141</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>44937</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>45849</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>46141</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>46141</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>45180</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>45426</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>44518</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>46150</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>46150</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17820,7 +17820,7 @@
         <v>46150</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>45546</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45106</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45194</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44862</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18185,7 +18185,7 @@
         <v>46161</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44953</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45188</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>46163</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45601</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45876</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45629</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>44901</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45876</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>46164</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45667</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44984</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45159</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>46171</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46174</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>45884</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19373,7 +19373,7 @@
         <v>46153</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>46183</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19519,7 +19519,7 @@
         <v>46183</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
         <v>46183</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>46183</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46183</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44928</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>46183</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46183</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>44805</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>45257</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45119</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>44883</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20322,7 +20322,7 @@
         <v>46155</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>45194</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45190</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>46196</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44956</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>44911</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45282</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>44517</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>44966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46206</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>44978</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44984</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>45215</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45058</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>45684</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>46258</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>46258</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>46171</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45344</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45058</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>46219</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21885,7 +21885,7 @@
         <v>44956</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>46219</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>44711</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45218</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>46227</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>46227</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22323,7 +22323,7 @@
         <v>46227</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>44618</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45293</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22542,7 +22542,7 @@
         <v>45181</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>45208</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>46241</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45614</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>46241</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>44951</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45187</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45187</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45295</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>44966</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45061</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23350,7 +23350,7 @@
         <v>45684</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23423,7 +23423,7 @@
         <v>46248</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45215</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45295</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45489</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>44890</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45239</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>45055</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45692</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>45250</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24241,7 +24241,7 @@
         <v>45181</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45926</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45586</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>44965</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>45737</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24684,7 +24684,7 @@
         <v>45174</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>44572</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24830,7 +24830,7 @@
         <v>44593</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24903,7 +24903,7 @@
         <v>45737</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>44753</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45595</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45174</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25200,7 +25200,7 @@
         <v>45297</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>45379</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44888</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>45194</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>45180</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45687</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25716,7 +25716,7 @@
         <v>45197</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25789,7 +25789,7 @@
         <v>45055</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>45297</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>45701</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26008,7 +26008,7 @@
         <v>45737</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45737</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26164,7 +26164,7 @@
         <v>45700</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>44984</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45610</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>45567</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45246</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26529,7 +26529,7 @@
         <v>45426</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26602,7 +26602,7 @@
         <v>45195</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26675,7 +26675,7 @@
         <v>46168</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44866</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>46164</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45211</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>44973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>46028</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46061</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45447</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45490</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>46283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44890</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44692</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>44481</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44862</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44874</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44480</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44627</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44685</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44831</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44567</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>44721</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44722</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44540</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45245</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>45504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45058</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>45737</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>45093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44917</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>45169</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44901</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>45180</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45297</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44517</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45684</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45194</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45028</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45218</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45190</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45265</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45231</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44588</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45489</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44984</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>44984</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44508</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45376</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45279</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44965</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45188</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45257</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45174</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44966</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45208</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45891</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44979</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45295</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45687</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44900</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44964</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45667</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45700</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45180</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45399</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45504</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45504</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45435</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45379</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45692</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45222</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45184</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45742</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45546</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44984</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45923</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45504</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45222</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45926</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45926</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45792</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45926</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45926</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45926</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44862</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44911</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>44813</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45257</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45614</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45191</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45797</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45737</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45737</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45797</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45159</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45685</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45344</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45093</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44994</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45055</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44572</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45684</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45315</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45293</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45817</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45817</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45215</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45736</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45818</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45190</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44593</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45701</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>44956</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44958</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44618</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44711</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45211</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45106</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45197</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45684</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45239</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45961</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45250</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45250</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45187</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44956</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45169</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45663</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45159</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45159</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45159</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45849</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45849</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44754</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44495</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45297</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45586</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45254</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45751</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45876</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45190</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44883</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44953</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45058</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45055</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44865</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45187</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46100</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44775</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45194</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44965</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45218</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46111</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46111</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45426</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44531</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45282</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45194</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44951</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45215</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46003</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46003</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46003</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46003</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45926</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44518</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45926</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46008</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46136</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45734</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46134</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>46008</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45180</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45756</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44753</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44861</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45061</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45782</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46139</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45097</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46139</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45218</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46050</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46141</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>46141</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>46141</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>46055</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46055</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46055</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46062</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46059</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45849</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46062</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>46061</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46062</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46059</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>46150</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>46069</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>46150</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>46084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46084</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46163</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>46164</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>46171</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46174</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46183</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>46183</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>46183</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>46183</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>46183</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>46206</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>46171</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>46219</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46219</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>46227</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>46227</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>46227</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>46241</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>46241</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>46248</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45926</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>46258</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46258</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>46300</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46111</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45908</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46150</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45610</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45567</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45246</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45426</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45195</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>46168</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>44866</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>46161</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44761</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>46164</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>45063</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>45211</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>44973</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>45875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>46028</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46061</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>45447</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>45490</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45601</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>46283</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>46168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44890</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44692</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>44481</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44862</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44874</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44480</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44627</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44685</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44831</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44567</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44491</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         <v>44518</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44874</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>44721</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>44722</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>44537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44540</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>45245</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45119</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>45119</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>45504</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>45058</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>45737</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>45093</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45215</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>44917</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>45169</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>45169</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>44901</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>45119</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>45629</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         <v>45180</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7231,7 +7231,7 @@
         <v>45297</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44517</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45684</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>45194</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>45295</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>45106</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         <v>45028</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>45218</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         <v>44805</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45190</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45194</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>45119</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44928</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>44796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>45265</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45231</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>44588</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45586</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>45489</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44984</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>44984</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9071,7 +9071,7 @@
         <v>44508</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45376</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45279</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44965</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45188</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45257</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9582,7 +9582,7 @@
         <v>45174</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         <v>45365</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44966</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>45208</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45891</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>44979</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>45295</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>45687</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>44900</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>44964</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>45181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         <v>45667</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>45700</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         <v>45180</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>44937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45174</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45399</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>45504</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45504</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45435</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45379</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>45692</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45222</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45184</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45601</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45742</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45546</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45504</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45922</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45790</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44888</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>44984</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45923</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45923</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45504</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>45222</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45926</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45926</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45792</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>45926</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45926</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>45926</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44862</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44911</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>44813</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45257</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>45614</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         <v>45191</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45797</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45737</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45737</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>45797</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45159</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45181</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45685</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45097</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>45344</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45667</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45692</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13997,7 +13997,7 @@
         <v>45093</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44994</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>45055</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>45092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>44572</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>44736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45684</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>45315</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14654,7 +14654,7 @@
         <v>45293</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>45817</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45817</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45215</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>45736</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>45818</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45742</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>45119</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15248,7 +15248,7 @@
         <v>45190</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44593</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45701</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15467,7 +15467,7 @@
         <v>44956</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15540,7 +15540,7 @@
         <v>44958</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44618</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44711</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45211</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45106</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45197</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>45684</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16124,7 +16124,7 @@
         <v>45791</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45239</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>45961</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16348,7 +16348,7 @@
         <v>45250</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45250</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>45187</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>44956</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45169</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>45663</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44734</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45159</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>45159</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45159</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>44798</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45849</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>45974</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45849</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44754</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44495</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45297</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45586</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45254</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45701</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45751</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45876</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45190</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44883</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44953</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45058</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>45055</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>44865</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45187</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>46100</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44775</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45197</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45985</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45194</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>44965</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45218</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46111</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46111</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45426</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44531</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45282</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45194</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>44951</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45215</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>46003</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>46003</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>46003</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46003</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45926</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44518</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44890</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45926</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>46008</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>46136</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45734</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46134</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>46008</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45180</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45756</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45838</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44753</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44861</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45061</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>44978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>45782</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>46139</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45097</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46139</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>45090</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>45218</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46050</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46141</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>46141</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>46141</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>46055</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>46055</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46055</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>46062</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46059</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45849</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>46062</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>46061</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>46062</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>46059</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>46150</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>46069</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>46150</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>46079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>46084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46084</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46161</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>46163</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>46164</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>46171</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>46174</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>46153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>46183</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>46183</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>46183</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24136,7 +24136,7 @@
         <v>46183</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46183</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24282,7 +24282,7 @@
         <v>46183</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24355,7 +24355,7 @@
         <v>46183</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>46155</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>46196</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>46206</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>46171</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>46219</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46219</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>46227</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>46227</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>46227</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>46241</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>46241</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>46248</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45926</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>46258</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46258</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>46300</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46111</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45908</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46150</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45610</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45567</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45246</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45426</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45195</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>46168</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46164</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>44761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 7879-2023</t>
+          <t>A 7847-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2336,14 +2336,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44973</v>
+        <v>46061</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2359,500 +2359,501 @@
         <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Ekoxe
+Huggorm
+Vanlig snok</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/artfynd/A 7847-2026 artfynd.xlsx", "A 7847-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor/A 7847-2026 karta.png", "A 7847-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor_geotiff/A 7847-2026 georefererad karta.tif", "A 7847-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomål/A 7847-2026 FSC-klagomål.docx", "A 7847-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomålsmail/A 7847-2026 FSC-klagomål mail.docx", "A 7847-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsyn/A 7847-2026 tillsynsbegäran.docx", "A 7847-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsynsmail/A 7847-2026 tillsynsbegäran mail.docx", "A 7847-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 7879-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44973</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SÖDERKÖPING</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>2</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ask
 Korskovall</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/artfynd/A 7879-2023 artfynd.xlsx", "A 7879-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor/A 7879-2023 karta.png", "A 7879-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor_geotiff/A 7879-2023 georefererad karta.tif", "A 7879-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomål/A 7879-2023 FSC-klagomål.docx", "A 7879-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomålsmail/A 7879-2023 FSC-klagomål mail.docx", "A 7879-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsyn/A 7879-2023 tillsynsbegäran.docx", "A 7879-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsynsmail/A 7879-2023 tillsynsbegäran mail.docx", "A 7879-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 21648-2023</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45063</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>SÖDERKÖPING</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SÖDERKÖPING</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>3.2</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Hasselsnok
 Kopparödla</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/artfynd/A 21648-2023 artfynd.xlsx", "A 21648-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor/A 21648-2023 karta.png", "A 21648-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor_geotiff/A 21648-2023 georefererad karta.tif", "A 21648-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomål/A 21648-2023 FSC-klagomål.docx", "A 21648-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomålsmail/A 21648-2023 FSC-klagomål mail.docx", "A 21648-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsyn/A 21648-2023 tillsynsbegäran.docx", "A 21648-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsynsmail/A 21648-2023 tillsynsbegäran mail.docx", "A 21648-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 21042-2026</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>46146</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>SÖDERKÖPING</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>SÖDERKÖPING</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>0.7</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Gul dropplav
 Gulpudrad spiklav</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/artfynd/A 21042-2026 artfynd.xlsx", "A 21042-2026")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor/A 21042-2026 karta.png", "A 21042-2026")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor_geotiff/A 21042-2026 georefererad karta.tif", "A 21042-2026")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomål/A 21042-2026 FSC-klagomål.docx", "A 21042-2026")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomålsmail/A 21042-2026 FSC-klagomål mail.docx", "A 21042-2026")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsyn/A 21042-2026 tillsynsbegäran.docx", "A 21042-2026")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsynsmail/A 21042-2026 tillsynsbegäran mail.docx", "A 21042-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 394-2026</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>46028</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SÖDERKÖPING</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SÖDERKÖPING</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>2.4</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Tallticka
 Igelkottsröksvamp</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/artfynd/A 394-2026 artfynd.xlsx", "A 394-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor/A 394-2026 karta.png", "A 394-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor_geotiff/A 394-2026 georefererad karta.tif", "A 394-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomål/A 394-2026 FSC-klagomål.docx", "A 394-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomålsmail/A 394-2026 FSC-klagomål mail.docx", "A 394-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsyn/A 394-2026 tillsynsbegäran.docx", "A 394-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsynsmail/A 394-2026 tillsynsbegäran mail.docx", "A 394-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 7847-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46061</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46312</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>SÖDERKÖPING</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Huggorm
-Vanlig snok</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/artfynd/A 7847-2026 artfynd.xlsx", "A 7847-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor/A 7847-2026 karta.png", "A 7847-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/kartor_geotiff/A 7847-2026 georefererad karta.tif", "A 7847-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomål/A 7847-2026 FSC-klagomål.docx", "A 7847-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/klagomålsmail/A 7847-2026 FSC-klagomål mail.docx", "A 7847-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsyn/A 7847-2026 tillsynsbegäran.docx", "A 7847-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0582/tillsynsmail/A 7847-2026 tillsynsbegäran mail.docx", "A 7847-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
@@ -2873,7 +2874,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2983,7 +2984,7 @@
         <v>45875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3089,7 +3090,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3195,7 +3196,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3300,7 +3301,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3405,7 +3406,7 @@
         <v>44974</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3510,7 +3511,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3615,7 +3616,7 @@
         <v>45490</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3724,7 +3725,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3834,7 +3835,7 @@
         <v>45601</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3939,7 +3940,7 @@
         <v>46283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4049,7 +4050,7 @@
         <v>45447</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4160,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4264,7 +4265,7 @@
         <v>46168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4369,7 +4370,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4442,7 +4443,7 @@
         <v>44890</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4515,7 +4516,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4588,7 +4589,7 @@
         <v>44678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4661,7 +4662,7 @@
         <v>44692</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4739,7 +4740,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4812,7 +4813,7 @@
         <v>44874</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4885,7 +4886,7 @@
         <v>44627</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4958,7 +4959,7 @@
         <v>44685</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5031,7 +5032,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5104,7 +5105,7 @@
         <v>44882</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5177,7 +5178,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5250,7 +5251,7 @@
         <v>44722</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5323,7 +5324,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5396,7 +5397,7 @@
         <v>44721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5469,7 +5470,7 @@
         <v>44722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5542,7 +5543,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5615,7 +5616,7 @@
         <v>44537</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5688,7 +5689,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5761,7 +5762,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5834,7 +5835,7 @@
         <v>44540</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5907,7 +5908,7 @@
         <v>45092</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5980,7 +5981,7 @@
         <v>44508</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6053,7 +6054,7 @@
         <v>45093</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6126,7 +6127,7 @@
         <v>45218</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6199,7 +6200,7 @@
         <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6272,7 +6273,7 @@
         <v>45265</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6345,7 +6346,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6418,7 +6419,7 @@
         <v>45055</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6491,7 +6492,7 @@
         <v>45667</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6564,7 +6565,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6637,7 +6638,7 @@
         <v>45218</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6710,7 +6711,7 @@
         <v>44958</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6783,7 +6784,7 @@
         <v>45028</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6856,7 +6857,7 @@
         <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6929,7 +6930,7 @@
         <v>44736</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7002,7 +7003,7 @@
         <v>45663</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7075,7 +7076,7 @@
         <v>45090</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7148,7 +7149,7 @@
         <v>45190</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7221,7 +7222,7 @@
         <v>45245</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7294,7 +7295,7 @@
         <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7367,7 +7368,7 @@
         <v>45159</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7440,7 +7441,7 @@
         <v>44754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7513,7 +7514,7 @@
         <v>45754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7586,7 +7587,7 @@
         <v>44979</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7664,7 +7665,7 @@
         <v>44734</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7737,7 +7738,7 @@
         <v>45736</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7815,7 +7816,7 @@
         <v>45119</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7888,7 +7889,7 @@
         <v>45119</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7961,7 +7962,7 @@
         <v>45119</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8034,7 +8035,7 @@
         <v>44588</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8107,7 +8108,7 @@
         <v>45191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8180,7 +8181,7 @@
         <v>45190</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8253,7 +8254,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8326,7 +8327,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8404,7 +8405,7 @@
         <v>45194</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8477,7 +8478,7 @@
         <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8550,7 +8551,7 @@
         <v>44775</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8623,7 +8624,7 @@
         <v>45279</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8696,7 +8697,7 @@
         <v>45180</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8774,7 +8775,7 @@
         <v>46139</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8847,7 +8848,7 @@
         <v>45365</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8920,7 +8921,7 @@
         <v>45254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8993,7 +8994,7 @@
         <v>45926</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9066,7 +9067,7 @@
         <v>44965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9139,7 +9140,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9212,7 +9213,7 @@
         <v>45884</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9285,7 +9286,7 @@
         <v>45093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9358,7 +9359,7 @@
         <v>45106</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9431,7 +9432,7 @@
         <v>45926</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9504,7 +9505,7 @@
         <v>45119</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9577,7 +9578,7 @@
         <v>44964</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9650,7 +9651,7 @@
         <v>45891</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9723,7 +9724,7 @@
         <v>45159</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9796,7 +9797,7 @@
         <v>45159</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9869,7 +9870,7 @@
         <v>46136</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9942,7 +9943,7 @@
         <v>45734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10015,7 +10016,7 @@
         <v>46139</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10088,7 +10089,7 @@
         <v>45197</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10161,7 +10162,7 @@
         <v>46141</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10234,7 +10235,7 @@
         <v>46141</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10307,7 +10308,7 @@
         <v>45250</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10385,7 +10386,7 @@
         <v>44798</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10458,7 +10459,7 @@
         <v>45849</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10531,7 +10532,7 @@
         <v>46141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10604,7 +10605,7 @@
         <v>46141</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10677,7 +10678,7 @@
         <v>45742</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10750,7 +10751,7 @@
         <v>45376</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10823,7 +10824,7 @@
         <v>44900</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10896,7 +10897,7 @@
         <v>45169</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10969,7 +10970,7 @@
         <v>45169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11042,7 +11043,7 @@
         <v>45923</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11115,7 +11116,7 @@
         <v>45922</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11188,7 +11189,7 @@
         <v>44917</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11261,7 +11262,7 @@
         <v>45923</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11334,7 +11335,7 @@
         <v>45926</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11407,7 +11408,7 @@
         <v>45926</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11480,7 +11481,7 @@
         <v>45504</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11553,7 +11554,7 @@
         <v>45215</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11626,7 +11627,7 @@
         <v>45926</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11699,7 +11700,7 @@
         <v>45926</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11772,7 +11773,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11845,7 +11846,7 @@
         <v>45211</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11918,7 +11919,7 @@
         <v>46150</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11991,7 +11992,7 @@
         <v>46150</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12064,7 +12065,7 @@
         <v>44861</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12137,7 +12138,7 @@
         <v>45315</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12210,7 +12211,7 @@
         <v>44796</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12283,7 +12284,7 @@
         <v>45399</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12356,7 +12357,7 @@
         <v>45684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12429,7 +12430,7 @@
         <v>44531</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12502,7 +12503,7 @@
         <v>45701</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12575,7 +12576,7 @@
         <v>44937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12648,7 +12649,7 @@
         <v>46161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12721,7 +12722,7 @@
         <v>45961</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12794,7 +12795,7 @@
         <v>45180</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12872,7 +12873,7 @@
         <v>45426</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12945,7 +12946,7 @@
         <v>46163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13023,7 +13024,7 @@
         <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13096,7 +13097,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13169,7 +13170,7 @@
         <v>44518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13242,7 +13243,7 @@
         <v>45546</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13315,7 +13316,7 @@
         <v>45985</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13388,7 +13389,7 @@
         <v>45106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13461,7 +13462,7 @@
         <v>46164</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13539,7 +13540,7 @@
         <v>45194</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13612,7 +13613,7 @@
         <v>44862</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13685,7 +13686,7 @@
         <v>44953</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13758,7 +13759,7 @@
         <v>45188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13831,7 +13832,7 @@
         <v>45601</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13904,7 +13905,7 @@
         <v>45629</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13977,7 +13978,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14050,7 +14051,7 @@
         <v>46003</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14123,7 +14124,7 @@
         <v>45667</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14196,7 +14197,7 @@
         <v>46003</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14269,7 +14270,7 @@
         <v>46003</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14342,7 +14343,7 @@
         <v>46003</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14415,7 +14416,7 @@
         <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14493,7 +14494,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14571,7 +14572,7 @@
         <v>46008</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14644,7 +14645,7 @@
         <v>45159</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14717,7 +14718,7 @@
         <v>46008</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14790,7 +14791,7 @@
         <v>46174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14863,7 +14864,7 @@
         <v>44928</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14936,7 +14937,7 @@
         <v>44805</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15009,7 +15010,7 @@
         <v>45257</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15082,7 +15083,7 @@
         <v>45119</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15155,7 +15156,7 @@
         <v>46153</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15228,7 +15229,7 @@
         <v>44883</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15301,7 +15302,7 @@
         <v>45194</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15374,7 +15375,7 @@
         <v>45190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15447,7 +15448,7 @@
         <v>46050</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15525,7 +15526,7 @@
         <v>46055</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15598,7 +15599,7 @@
         <v>46055</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15671,7 +15672,7 @@
         <v>46055</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15744,7 +15745,7 @@
         <v>46055</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15822,7 +15823,7 @@
         <v>46056</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15895,7 +15896,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15968,7 +15969,7 @@
         <v>46183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16041,7 +16042,7 @@
         <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16114,7 +16115,7 @@
         <v>46059</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16187,7 +16188,7 @@
         <v>46059</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16260,7 +16261,7 @@
         <v>46183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16333,7 +16334,7 @@
         <v>46061</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16406,7 +16407,7 @@
         <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16479,7 +16480,7 @@
         <v>46062</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16552,7 +16553,7 @@
         <v>46062</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16625,7 +16626,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16698,7 +16699,7 @@
         <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16771,7 +16772,7 @@
         <v>46183</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16844,7 +16845,7 @@
         <v>44956</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16917,7 +16918,7 @@
         <v>44911</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16995,7 +16996,7 @@
         <v>46069</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17068,7 +17069,7 @@
         <v>45282</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17141,7 +17142,7 @@
         <v>44517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17219,7 +17220,7 @@
         <v>44966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17292,7 +17293,7 @@
         <v>46079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17370,7 +17371,7 @@
         <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17443,7 +17444,7 @@
         <v>46084</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17516,7 +17517,7 @@
         <v>44978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17594,7 +17595,7 @@
         <v>44984</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17672,7 +17673,7 @@
         <v>45215</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17745,7 +17746,7 @@
         <v>46155</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17823,7 +17824,7 @@
         <v>45058</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17896,7 +17897,7 @@
         <v>45684</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17969,7 +17970,7 @@
         <v>46196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18042,7 +18043,7 @@
         <v>46100</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18115,7 +18116,7 @@
         <v>45344</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18188,7 +18189,7 @@
         <v>45058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18261,7 +18262,7 @@
         <v>46106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18334,7 +18335,7 @@
         <v>46111</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18407,7 +18408,7 @@
         <v>46111</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18480,7 +18481,7 @@
         <v>44956</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18553,7 +18554,7 @@
         <v>44711</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18626,7 +18627,7 @@
         <v>45218</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18699,7 +18700,7 @@
         <v>44618</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18772,7 +18773,7 @@
         <v>45293</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18845,7 +18846,7 @@
         <v>45181</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18918,7 +18919,7 @@
         <v>46134</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18991,7 +18992,7 @@
         <v>45838</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19064,7 +19065,7 @@
         <v>45756</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19137,7 +19138,7 @@
         <v>46206</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19210,7 +19211,7 @@
         <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19283,7 +19284,7 @@
         <v>45208</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19361,7 +19362,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19439,7 +19440,7 @@
         <v>45614</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19512,7 +19513,7 @@
         <v>44951</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19585,7 +19586,7 @@
         <v>46219</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19658,7 +19659,7 @@
         <v>45187</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19731,7 +19732,7 @@
         <v>45187</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19804,7 +19805,7 @@
         <v>46219</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19877,7 +19878,7 @@
         <v>45295</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19950,7 +19951,7 @@
         <v>44966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20023,7 +20024,7 @@
         <v>46227</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20096,7 +20097,7 @@
         <v>46227</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20169,7 +20170,7 @@
         <v>46227</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20242,7 +20243,7 @@
         <v>45061</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20315,7 +20316,7 @@
         <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20388,7 +20389,7 @@
         <v>45215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20466,7 +20467,7 @@
         <v>45295</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20539,7 +20540,7 @@
         <v>45489</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20612,7 +20613,7 @@
         <v>44890</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20685,7 +20686,7 @@
         <v>45239</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20763,7 +20764,7 @@
         <v>45055</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20836,7 +20837,7 @@
         <v>45055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20909,7 +20910,7 @@
         <v>45169</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20982,7 +20983,7 @@
         <v>45250</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21060,7 +21061,7 @@
         <v>45181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21133,7 +21134,7 @@
         <v>46241</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21206,7 +21207,7 @@
         <v>45586</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21279,7 +21280,7 @@
         <v>44994</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21352,7 +21353,7 @@
         <v>44965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21425,7 +21426,7 @@
         <v>45737</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21503,7 +21504,7 @@
         <v>46241</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21576,7 +21577,7 @@
         <v>45174</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21649,7 +21650,7 @@
         <v>44572</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21722,7 +21723,7 @@
         <v>44593</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21795,7 +21796,7 @@
         <v>45737</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21873,7 +21874,7 @@
         <v>44753</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21946,7 +21947,7 @@
         <v>45595</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22019,7 +22020,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22092,7 +22093,7 @@
         <v>45174</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22165,7 +22166,7 @@
         <v>45297</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22238,7 +22239,7 @@
         <v>45379</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22311,7 +22312,7 @@
         <v>45097</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22384,7 +22385,7 @@
         <v>44888</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22457,7 +22458,7 @@
         <v>45194</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22530,7 +22531,7 @@
         <v>45180</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22608,7 +22609,7 @@
         <v>45687</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22681,7 +22682,7 @@
         <v>45197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22754,7 +22755,7 @@
         <v>45055</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22827,7 +22828,7 @@
         <v>45297</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22900,7 +22901,7 @@
         <v>45926</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22973,7 +22974,7 @@
         <v>45701</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23046,7 +23047,7 @@
         <v>45737</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23124,7 +23125,7 @@
         <v>46258</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23197,7 +23198,7 @@
         <v>46300</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23270,7 +23271,7 @@
         <v>45700</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23343,7 +23344,7 @@
         <v>44984</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23416,7 +23417,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23489,7 +23490,7 @@
         <v>46111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23562,7 +23563,7 @@
         <v>45504</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23635,7 +23636,7 @@
         <v>45504</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23708,7 +23709,7 @@
         <v>45908</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23781,7 +23782,7 @@
         <v>45435</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23854,7 +23855,7 @@
         <v>45601</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23927,7 +23928,7 @@
         <v>45692</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24000,7 +24001,7 @@
         <v>45504</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24073,7 +24074,7 @@
         <v>45504</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24146,7 +24147,7 @@
         <v>45184</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24219,7 +24220,7 @@
         <v>45790</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24292,7 +24293,7 @@
         <v>46150</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24365,7 +24366,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24438,7 +24439,7 @@
         <v>45792</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24511,7 +24512,7 @@
         <v>45257</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24584,7 +24585,7 @@
         <v>45797</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24657,7 +24658,7 @@
         <v>45797</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24730,7 +24731,7 @@
         <v>46305</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24803,7 +24804,7 @@
         <v>45685</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24876,7 +24877,7 @@
         <v>45692</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24949,7 +24950,7 @@
         <v>44939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25022,7 +25023,7 @@
         <v>45742</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25095,7 +25096,7 @@
         <v>45817</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25168,7 +25169,7 @@
         <v>45817</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25241,7 +25242,7 @@
         <v>45818</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25314,7 +25315,7 @@
         <v>45791</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25387,7 +25388,7 @@
         <v>45849</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25460,7 +25461,7 @@
         <v>45849</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25533,7 +25534,7 @@
         <v>45586</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25606,7 +25607,7 @@
         <v>45876</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25679,7 +25680,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25752,7 +25753,7 @@
         <v>45610</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25825,7 +25826,7 @@
         <v>45567</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25898,7 +25899,7 @@
         <v>45246</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25971,7 +25972,7 @@
         <v>45426</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26044,7 +26045,7 @@
         <v>45195</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26117,7 +26118,7 @@
         <v>46168</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45244</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>46161</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46164</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>44761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>46061</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45063</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>46146</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>46028</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45211</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45295</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44974</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45478</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>45490</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>45601</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46283</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45447</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>44890</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44692</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>44874</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44627</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>44685</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44882</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44722</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44491</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44721</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44722</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44874</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44537</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44518</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44540</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>45092</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>44508</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>45093</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45218</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>45265</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44495</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45055</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>45667</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45218</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44958</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>45028</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>45265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44736</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>45663</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>45090</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>45190</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45245</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45222</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45159</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44979</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>44734</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45736</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45119</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45119</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>45119</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44588</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>45191</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45190</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45231</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44813</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45194</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45174</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>44775</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45279</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45180</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>46139</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45365</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45254</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45926</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44965</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44865</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>45884</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>45093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>45106</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>45926</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>45119</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44964</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45891</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         <v>45159</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45159</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         <v>46136</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>45734</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>46139</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>45197</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>46141</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>46141</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45250</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44798</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>45849</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>46141</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>46141</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45742</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45376</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44900</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45169</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>45923</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45922</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44917</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45923</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11335,7 +11335,7 @@
         <v>45926</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>45926</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45504</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45215</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45926</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11700,7 +11700,7 @@
         <v>45926</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>45926</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>45211</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>46150</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>46150</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44861</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45315</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44796</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45399</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44531</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45701</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>44937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>46161</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>45961</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>45180</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45426</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>46163</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45974</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45974</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44518</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45546</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45985</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45106</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>46164</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45194</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44862</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>44953</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45188</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>45601</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45629</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44901</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>46003</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45667</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>46003</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>46003</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>46003</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14416,7 +14416,7 @@
         <v>46171</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>44984</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46008</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45159</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>46008</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46174</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>44928</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44805</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45257</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>45119</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>46153</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44883</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         <v>45194</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>46050</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>46055</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46055</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>46055</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>46055</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>46056</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15969,7 +15969,7 @@
         <v>46183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>46183</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>46059</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>46059</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>46183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>46061</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>46183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46062</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>46062</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>46062</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>46183</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16845,7 +16845,7 @@
         <v>44956</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44911</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>46069</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17069,7 +17069,7 @@
         <v>45282</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17142,7 +17142,7 @@
         <v>44517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>44966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46079</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>46084</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>46084</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>44978</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44984</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45215</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46155</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45058</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17897,7 +17897,7 @@
         <v>45684</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>46196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>46100</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45344</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>46106</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>46111</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>46111</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44956</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44711</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45218</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>44618</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45293</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45181</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>46134</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18992,7 +18992,7 @@
         <v>45838</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>45756</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>46206</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>45208</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46171</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45614</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44951</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>46219</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>45187</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19732,7 +19732,7 @@
         <v>45187</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19805,7 +19805,7 @@
         <v>46219</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45295</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         <v>44966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>46227</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20097,7 +20097,7 @@
         <v>46227</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>46227</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20243,7 +20243,7 @@
         <v>45061</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45684</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45215</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45295</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45489</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>44890</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45239</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45055</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45055</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>45169</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>45250</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21061,7 +21061,7 @@
         <v>45181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>46241</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45586</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>44994</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>44965</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45737</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>46241</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45174</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44572</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>44593</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45737</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>44753</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45595</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>46248</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45174</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45297</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45379</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45097</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44888</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45194</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45180</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22609,7 +22609,7 @@
         <v>45687</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22755,7 +22755,7 @@
         <v>45055</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45297</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45926</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45701</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>45737</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>46258</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46300</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>45700</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>44984</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45222</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46111</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45504</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45504</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45908</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45435</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45601</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45692</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45504</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45504</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45184</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45790</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>46150</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46258</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45792</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45257</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45797</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45797</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>46305</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45685</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45692</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44939</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45742</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45817</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45817</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45818</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45791</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45849</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45849</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45586</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45876</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45610</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45567</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45246</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45426</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45195</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>46168</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>46161</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46164</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>44761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>46061</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>46028</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>45875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45211</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45601</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45295</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44974</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>44890</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44692</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>44874</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44627</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>44685</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44882</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44722</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44721</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44874</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44537</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>44540</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44890</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45737</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45891</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45180</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44753</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45061</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45884</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44978</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>46163</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45922</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45923</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45923</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45926</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45926</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>46171</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>45090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45218</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45245</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>46174</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45119</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45119</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>46153</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45297</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44805</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45504</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45058</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46183</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>46183</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44901</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>46183</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>46183</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>46183</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46183</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45629</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45180</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45194</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45295</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45028</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45218</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45961</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45055</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45190</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45194</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>46155</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>44928</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>44796</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>46196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45974</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45595</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44508</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45376</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44965</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45188</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45257</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45208</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45489</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45687</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44984</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44984</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>46219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46219</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45667</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45700</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46003</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>46227</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46227</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>46227</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>46003</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>46003</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>46003</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>46008</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45504</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45504</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45435</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45692</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45222</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45184</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45601</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45504</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45790</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44984</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45504</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45792</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46241</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>46241</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45257</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45797</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45797</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>46050</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45685</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46055</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46055</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46055</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46056</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46055</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>46248</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>46062</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46059</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>46062</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>46062</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46059</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45817</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45818</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45742</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>46069</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>46079</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46084</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46084</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45926</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45174</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45365</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46100</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>46258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45849</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45849</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>46106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44979</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45295</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>46258</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>46111</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45586</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>46111</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>46150</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45876</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45876</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44900</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45926</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>46305</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45926</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>46136</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45734</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>46134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45756</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45838</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45742</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45546</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45782</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>44888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46139</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>44911</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>46141</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46141</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45614</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46141</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45849</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45344</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46150</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46150</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44994</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>44572</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44736</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45315</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45293</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45736</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44956</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44958</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45106</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>44956</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45663</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44734</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45159</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>44798</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44495</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45701</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45751</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45190</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>44953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45055</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44865</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45426</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44517</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45684</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44966</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45586</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44966</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45601</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>45180</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45174</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45399</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45379</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44862</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44813</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45737</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45737</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45159</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45181</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45097</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45667</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45093</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45055</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45092</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45684</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45215</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45119</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45190</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44593</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45701</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44618</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44711</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45211</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45197</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45684</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45239</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45250</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45250</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45187</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45169</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45159</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44754</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45297</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45254</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45265</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44883</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45187</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44775</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45197</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45194</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45218</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45194</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44951</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45215</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45610</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45567</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45246</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45426</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45195</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>46168</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>

--- a/Översikt SÖDERKÖPING.xlsx
+++ b/Översikt SÖDERKÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>44866</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         <v>46161</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>44866</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>46185</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44644</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>46259</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>46161</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>45244</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>46259</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>45569</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         <v>46168</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>46185</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>46164</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>44761</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>46061</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>44973</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>46028</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>45875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2874,7 +2874,7 @@
         <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45211</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>44841</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>45601</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>45478</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>45490</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
         <v>46283</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>46079</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45295</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45447</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>44974</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46168</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>44862</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>44890</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44678</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44692</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44862</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>44874</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>44627</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
         <v>44685</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>44831</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>44882</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>44567</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         <v>44722</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44721</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5397,7 +5397,7 @@
         <v>44722</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44874</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44537</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44518</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>44861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>44540</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>44518</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>44890</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45737</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45891</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45180</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44753</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45231</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>45061</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45884</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>46161</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44978</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>46163</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>46164</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>45922</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45923</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>45923</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>45926</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7174,7 +7174,7 @@
         <v>45926</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>45926</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>45926</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45926</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         <v>46171</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>45090</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>45218</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7763,7 +7763,7 @@
         <v>45093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7836,7 +7836,7 @@
         <v>45245</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7909,7 +7909,7 @@
         <v>46174</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45119</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45119</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>46153</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         <v>45297</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>45106</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>44805</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>45504</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45058</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8566,7 +8566,7 @@
         <v>45119</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         <v>45169</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>46183</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>46183</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44901</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>46183</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>46183</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>46183</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46183</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45629</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>46183</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45180</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>45194</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9666,7 +9666,7 @@
         <v>45295</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45028</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>45218</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>45961</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>45055</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45055</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45190</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45194</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>46155</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>44928</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>44796</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>45265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>44588</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>46196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>45974</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>45595</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44508</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10985,7 +10985,7 @@
         <v>45376</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44965</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>45188</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45257</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45208</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45985</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45489</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45687</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44984</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44984</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
         <v>46219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>46219</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45667</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45700</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>46003</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>46227</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46227</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>46227</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>46003</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>46003</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>46003</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         <v>46008</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>46008</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>45504</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45504</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45435</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45692</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45222</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45184</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45601</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45504</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>45790</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>44984</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         <v>45504</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>45792</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46241</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>46241</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>45257</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45797</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45797</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>46050</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45685</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45692</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>46055</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46055</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46055</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46056</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>46055</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>46248</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>46062</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>46059</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>46062</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>46061</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>46062</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>46059</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45817</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45817</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45818</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45742</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>46069</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15760,7 +15760,7 @@
         <v>46079</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46084</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46084</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45791</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>45926</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45174</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45365</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>46100</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>46258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45849</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>45849</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>46106</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>44979</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45295</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16792,7 +16792,7 @@
         <v>46258</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>46300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>46111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>46111</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
         <v>45586</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>46111</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>46150</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17376,7 +17376,7 @@
         <v>45876</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45876</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>44900</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>45926</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         <v>46305</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45926</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>46136</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17887,7 +17887,7 @@
         <v>45734</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>46134</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45756</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>45838</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18179,7 +18179,7 @@
         <v>45742</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>45546</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>45782</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>44888</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46139</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45222</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>46139</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>44911</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>46141</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>46141</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46141</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45614</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46141</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45849</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45344</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>46150</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46150</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>44994</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>44572</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44736</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>45315</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45293</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45736</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44956</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>44958</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45106</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>44956</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>45663</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>44734</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45159</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20379,7 +20379,7 @@
         <v>44798</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20452,7 +20452,7 @@
         <v>44495</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20525,7 +20525,7 @@
         <v>45701</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20598,7 +20598,7 @@
         <v>45751</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45190</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>44953</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45058</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45055</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>44865</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>45426</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21109,7 +21109,7 @@
         <v>45754</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>45119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21255,7 +21255,7 @@
         <v>44517</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45684</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>44966</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45586</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>44966</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21625,7 +21625,7 @@
         <v>45601</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>44964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>45180</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>45174</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45399</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45379</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44862</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>44813</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45191</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45737</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45737</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45159</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45181</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45097</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45667</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45093</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45055</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>45092</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>45684</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45215</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45119</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45190</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>44593</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45701</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44618</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>44711</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45211</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45197</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45684</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45174</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45239</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45250</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>45250</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45187</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45169</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45159</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45159</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>44754</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45297</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45254</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45265</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44883</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45187</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>44775</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45197</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45194</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>44965</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45218</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45282</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45194</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>44951</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45215</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45610</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45567</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45246</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45426</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45195</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>46168</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
